--- a/MiniTemplate/Datas/work.xlsx
+++ b/MiniTemplate/Datas/work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B1FFAC0-2D46-4352-A427-5C6035913D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5CDF5C-2E92-43B2-B7E7-49CB7B2F4E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
+    <workbookView xWindow="1056" yWindow="24" windowWidth="30696" windowHeight="16536" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="95">
   <si>
     <t>##var</t>
   </si>
@@ -307,6 +307,22 @@
   </si>
   <si>
     <t>机遇零工：传奇机遇。完成后可获得金币报酬。</t>
+  </si>
+  <si>
+    <t>isUseItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否消耗 unlockItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -682,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD355D9D-C98C-47AD-A1A7-799954E007DF}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -694,9 +710,10 @@
     <col min="7" max="8" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -727,8 +744,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -759,8 +779,11 @@
       <c r="J2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -791,8 +814,11 @@
       <c r="J3" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -823,784 +849,781 @@
       <c r="J4" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="K4" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5">
         <v>10001</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>200</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>10</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="I5">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>10002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6">
+        <v>300</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>10003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>400</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>10004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8">
+        <v>500</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>10005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9">
+        <v>600</v>
+      </c>
+      <c r="H9">
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>10006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10">
+        <v>250</v>
+      </c>
+      <c r="H10">
+        <v>11</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>10007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11">
+        <v>350</v>
+      </c>
+      <c r="H11">
+        <v>16</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>10008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12">
+        <v>450</v>
+      </c>
+      <c r="H12">
+        <v>21</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>10009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13">
+        <v>550</v>
+      </c>
+      <c r="H13">
+        <v>26</v>
+      </c>
+      <c r="I13">
+        <v>4</v>
+      </c>
+      <c r="J13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>10010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14">
+        <v>650</v>
+      </c>
+      <c r="H14">
+        <v>31</v>
+      </c>
+      <c r="I14">
+        <v>5</v>
+      </c>
+      <c r="J14">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>10011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15">
+        <v>300</v>
+      </c>
+      <c r="H15">
+        <v>12</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>10012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16">
+        <v>400</v>
+      </c>
+      <c r="H16">
+        <v>17</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>10013</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17">
+        <v>500</v>
+      </c>
+      <c r="H17">
+        <v>22</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>10014</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18">
+        <v>600</v>
+      </c>
+      <c r="H18">
+        <v>27</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="J18">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>10015</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19">
+        <v>700</v>
+      </c>
+      <c r="H19">
+        <v>32</v>
+      </c>
+      <c r="I19">
+        <v>5</v>
+      </c>
+      <c r="J19">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>10016</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>350</v>
+      </c>
+      <c r="H20">
+        <v>13</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>10017</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21">
+        <v>450</v>
+      </c>
+      <c r="H21">
+        <v>18</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>10018</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22">
+        <v>550</v>
+      </c>
+      <c r="H22">
+        <v>23</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>10019</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23">
+        <v>650</v>
+      </c>
+      <c r="H23">
+        <v>28</v>
+      </c>
+      <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="J23">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>10020</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24">
+        <v>750</v>
+      </c>
+      <c r="H24">
+        <v>33</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>10002</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>10021</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25">
+        <v>400</v>
+      </c>
+      <c r="H25">
+        <v>14</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>10022</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26">
+        <v>500</v>
+      </c>
+      <c r="H26">
+        <v>19</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>10023</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27">
+        <v>600</v>
+      </c>
+      <c r="H27">
+        <v>24</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>10024</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28">
+        <v>700</v>
+      </c>
+      <c r="H28">
+        <v>29</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>10025</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29">
+        <v>800</v>
+      </c>
+      <c r="H29">
+        <v>34</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>10026</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30">
+        <v>450</v>
+      </c>
+      <c r="H30">
+        <v>15</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>10027</v>
+      </c>
+      <c r="C31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31">
+        <v>550</v>
+      </c>
+      <c r="H31">
+        <v>20</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>10028</v>
+      </c>
+      <c r="C32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32">
+        <v>650</v>
+      </c>
+      <c r="H32">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6">
-        <v>300</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>10029</v>
+      </c>
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33">
+        <v>750</v>
+      </c>
+      <c r="H33">
+        <v>30</v>
+      </c>
+      <c r="I33">
+        <v>4</v>
+      </c>
+      <c r="J33">
         <v>1001</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>10003</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7">
-        <v>400</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>10004</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8">
-        <v>500</v>
-      </c>
-      <c r="G8">
-        <v>25</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>10005</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>10030</v>
+      </c>
+      <c r="C34" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34">
+        <v>850</v>
+      </c>
+      <c r="H34">
         <v>35</v>
       </c>
-      <c r="F9">
-        <v>600</v>
-      </c>
-      <c r="G9">
-        <v>30</v>
-      </c>
-      <c r="H9">
+      <c r="I34">
         <v>5</v>
       </c>
-      <c r="I9">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>10006</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10">
-        <v>250</v>
-      </c>
-      <c r="G10">
-        <v>11</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10007</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11">
-        <v>350</v>
-      </c>
-      <c r="G11">
-        <v>16</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10008</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12">
-        <v>450</v>
-      </c>
-      <c r="G12">
-        <v>21</v>
-      </c>
-      <c r="H12">
-        <v>3</v>
-      </c>
-      <c r="I12">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>10009</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13">
-        <v>550</v>
-      </c>
-      <c r="G13">
-        <v>26</v>
-      </c>
-      <c r="H13">
-        <v>4</v>
-      </c>
-      <c r="I13">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>10010</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14">
-        <v>650</v>
-      </c>
-      <c r="G14">
-        <v>31</v>
-      </c>
-      <c r="H14">
-        <v>5</v>
-      </c>
-      <c r="I14">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>10011</v>
-      </c>
-      <c r="B15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15">
-        <v>300</v>
-      </c>
-      <c r="G15">
-        <v>12</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>10012</v>
-      </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16">
-        <v>400</v>
-      </c>
-      <c r="G16">
-        <v>17</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-      <c r="I16">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>10013</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17">
-        <v>500</v>
-      </c>
-      <c r="G17">
-        <v>22</v>
-      </c>
-      <c r="H17">
-        <v>3</v>
-      </c>
-      <c r="I17">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>10014</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18">
-        <v>600</v>
-      </c>
-      <c r="G18">
-        <v>27</v>
-      </c>
-      <c r="H18">
-        <v>4</v>
-      </c>
-      <c r="I18">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>10015</v>
-      </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19">
-        <v>700</v>
-      </c>
-      <c r="G19">
-        <v>32</v>
-      </c>
-      <c r="H19">
-        <v>5</v>
-      </c>
-      <c r="I19">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>10016</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20">
-        <v>350</v>
-      </c>
-      <c r="G20">
-        <v>13</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>10017</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21">
-        <v>450</v>
-      </c>
-      <c r="G21">
-        <v>18</v>
-      </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
-      <c r="I21">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>10018</v>
-      </c>
-      <c r="B22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22">
-        <v>550</v>
-      </c>
-      <c r="G22">
-        <v>23</v>
-      </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-      <c r="I22">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>10019</v>
-      </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23">
-        <v>650</v>
-      </c>
-      <c r="G23">
-        <v>28</v>
-      </c>
-      <c r="H23">
-        <v>4</v>
-      </c>
-      <c r="I23">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>10020</v>
-      </c>
-      <c r="B24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24">
-        <v>750</v>
-      </c>
-      <c r="G24">
-        <v>33</v>
-      </c>
-      <c r="H24">
-        <v>5</v>
-      </c>
-      <c r="I24">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>10021</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25">
-        <v>400</v>
-      </c>
-      <c r="G25">
-        <v>14</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>10022</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26">
-        <v>500</v>
-      </c>
-      <c r="G26">
-        <v>19</v>
-      </c>
-      <c r="H26">
-        <v>2</v>
-      </c>
-      <c r="I26">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>10023</v>
-      </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27">
-        <v>600</v>
-      </c>
-      <c r="G27">
-        <v>24</v>
-      </c>
-      <c r="H27">
-        <v>3</v>
-      </c>
-      <c r="I27">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>10024</v>
-      </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" t="s">
-        <v>77</v>
-      </c>
-      <c r="F28">
-        <v>700</v>
-      </c>
-      <c r="G28">
-        <v>29</v>
-      </c>
-      <c r="H28">
-        <v>4</v>
-      </c>
-      <c r="I28">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>10025</v>
-      </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29">
-        <v>800</v>
-      </c>
-      <c r="G29">
-        <v>34</v>
-      </c>
-      <c r="H29">
-        <v>5</v>
-      </c>
-      <c r="I29">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>10026</v>
-      </c>
-      <c r="B30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30">
-        <v>450</v>
-      </c>
-      <c r="G30">
-        <v>15</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>10027</v>
-      </c>
-      <c r="B31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31">
-        <v>550</v>
-      </c>
-      <c r="G31">
-        <v>20</v>
-      </c>
-      <c r="H31">
-        <v>2</v>
-      </c>
-      <c r="I31">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>10028</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32">
-        <v>650</v>
-      </c>
-      <c r="G32">
-        <v>25</v>
-      </c>
-      <c r="H32">
-        <v>3</v>
-      </c>
-      <c r="I32">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>10029</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>87</v>
-      </c>
-      <c r="D33" t="s">
-        <v>88</v>
-      </c>
-      <c r="F33">
-        <v>750</v>
-      </c>
-      <c r="G33">
-        <v>30</v>
-      </c>
-      <c r="H33">
-        <v>4</v>
-      </c>
-      <c r="I33">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>10030</v>
-      </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
-        <v>90</v>
-      </c>
-      <c r="F34">
-        <v>850</v>
-      </c>
-      <c r="G34">
-        <v>35</v>
-      </c>
-      <c r="H34">
-        <v>5</v>
-      </c>
-      <c r="I34">
+      <c r="J34">
         <v>1010</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/work.xlsx
+++ b/MiniTemplate/Datas/work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5CDF5C-2E92-43B2-B7E7-49CB7B2F4E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F3EC94-2AF6-4F26-B189-7DB2CF5C8222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1056" yWindow="24" windowWidth="30696" windowHeight="16536" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="99">
   <si>
     <t>##var</t>
   </si>
@@ -117,199 +117,252 @@
     <t>搬运杂物</t>
   </si>
   <si>
-    <t>基础劳务零工：搬运杂物。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>仓库分拣</t>
   </si>
   <si>
-    <t>基础劳务零工：仓库分拣。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>街区派送</t>
   </si>
   <si>
-    <t>基础劳务零工：街区派送。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>夜班装卸</t>
   </si>
   <si>
-    <t>基础劳务零工：夜班装卸。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>展会搭建</t>
   </si>
   <si>
-    <t>基础劳务零工：展会搭建。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>设计</t>
   </si>
   <si>
     <t>海报排版</t>
   </si>
   <si>
-    <t>设计零工：海报排版。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>图标绘制</t>
   </si>
   <si>
-    <t>设计零工：图标绘制。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>宣传页设计</t>
   </si>
   <si>
-    <t>设计零工：宣传页设计。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>品牌视觉提案</t>
   </si>
   <si>
-    <t>设计零工：品牌视觉提案。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>展台主视觉设计</t>
   </si>
   <si>
-    <t>设计零工：展台主视觉设计。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>程序</t>
   </si>
   <si>
-    <t>脚本修补</t>
-  </si>
-  <si>
-    <t>程序零工：脚本修补。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>网页组件开发</t>
-  </si>
-  <si>
-    <t>程序零工：网页组件开发。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>数据工具编写</t>
-  </si>
-  <si>
-    <t>程序零工：数据工具编写。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>功能模块开发</t>
-  </si>
-  <si>
-    <t>程序零工：功能模块开发。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>系统性能优化</t>
-  </si>
-  <si>
-    <t>程序零工：系统性能优化。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>维修</t>
   </si>
   <si>
     <t>家电检修</t>
   </si>
   <si>
-    <t>维修零工：家电检修。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>水管维护</t>
   </si>
   <si>
-    <t>维修零工：水管维护。完成后可获得金币报酬。</t>
-  </si>
-  <si>
     <t>电路排查</t>
   </si>
   <si>
-    <t>维修零工：电路排查。完成后可获得金币报酬。</t>
+    <t>写作</t>
+  </si>
+  <si>
+    <t>短文撰写</t>
+  </si>
+  <si>
+    <t>产品文案</t>
+  </si>
+  <si>
+    <t>专题报道</t>
+  </si>
+  <si>
+    <t>剧本创作</t>
+  </si>
+  <si>
+    <t>长篇策划案</t>
+  </si>
+  <si>
+    <t>机遇</t>
+  </si>
+  <si>
+    <t>临时委托</t>
+  </si>
+  <si>
+    <t>限时合作</t>
+  </si>
+  <si>
+    <t>特别邀约</t>
+  </si>
+  <si>
+    <t>稀有项目</t>
+  </si>
+  <si>
+    <t>传奇机遇</t>
+  </si>
+  <si>
+    <t>isUseItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否消耗 unlockItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>城市睡了，货车醒了，搬完最后一箱，天也差不多亮了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>目的地通常在没有电梯的那栋楼里</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界暂时有了秩序，至少这一排货架是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把解释藏进一个一眼就懂的小小轮廓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>甲方觉得它还可以再活泼一点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页开发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小程序开发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AAA游戏开发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库维护</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大数据开发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把散落的生活搬到新的位置，双手会记得每一只箱子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用一晚拼起明天的热闹，散场后再将它轻轻收好</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>让文字站到合适的位置，替消息喊得远一点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把许多想说的话，折进一张会发光的页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在来往的人潮中央，竖起一面能被目光找到的旗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>种下按钮与窗口，让沉睡的页面听懂点击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在数字海洋里打捞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搭建一座庞大世界，从第一块地砖忙到最后一片云</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>替无数记忆看守抽屉，别把钥匙放错格子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把日常小事装进口袋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>倾听机器的小声抱怨，再让熟悉的嗡鸣重新响起</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沿着滴答声寻找源头，阻止客厅提前进入雨季</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>光只是暂时迷了路，顺着线路把它领回灯里</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>精密仪器修复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把沉默的大家伙拆成零件，再唤醒它沉睡的力气</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>设备大修</t>
-  </si>
-  <si>
-    <t>维修零工：设备大修。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>精密仪器修复</t>
-  </si>
-  <si>
-    <t>维修零工：精密仪器修复。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>写作</t>
-  </si>
-  <si>
-    <t>短文撰写</t>
-  </si>
-  <si>
-    <t>写作零工：短文撰写。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>产品文案</t>
-  </si>
-  <si>
-    <t>写作零工：产品文案。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>专题报道</t>
-  </si>
-  <si>
-    <t>写作零工：专题报道。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>剧本创作</t>
-  </si>
-  <si>
-    <t>写作零工：剧本创作。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>长篇策划案</t>
-  </si>
-  <si>
-    <t>写作零工：长篇策划案。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>机遇</t>
-  </si>
-  <si>
-    <t>临时委托</t>
-  </si>
-  <si>
-    <t>机遇零工：临时委托。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>限时合作</t>
-  </si>
-  <si>
-    <t>机遇零工：限时合作。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>特别邀约</t>
-  </si>
-  <si>
-    <t>机遇零工：特别邀约。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>稀有项目</t>
-  </si>
-  <si>
-    <t>机遇零工：稀有项目。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>传奇机遇</t>
-  </si>
-  <si>
-    <t>机遇零工：传奇机遇。完成后可获得金币报酬。</t>
-  </si>
-  <si>
-    <t>isUseItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在细小刻度之间保持耐心，让时间重新准确行走</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将一个小小念头铺成几行字，刚好够装下一段心情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>为普通物件找到一句好话，让它看起来更值得被选择</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>收集散落在人群中的声音，把它们拼成一段完整故事</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>从一个模糊念头出发，慢慢画出通往结果的长地图</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>为尚未见面的人安排相遇，也替他们准备一点小麻烦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划之外传来敲门声，一件小事正等着合适的人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机会只会停留片刻，出发之前最好别想得太久</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有人越过人群想起了你，或许该去看看门后有什么</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平常的日程裂开一道亮光，里面藏着不平常的挑战</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>命运递来一张没有地址的车票，远方正好还有空位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>coinRewardSection</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -321,7 +374,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>是否消耗 unlockItem</t>
+    <t>金币数浮动区间百分比</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -329,7 +382,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,6 +404,14 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -377,11 +438,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -698,22 +762,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD355D9D-C98C-47AD-A1A7-799954E007DF}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.6640625" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="54.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" customWidth="1"/>
+    <col min="8" max="9" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.109375" customWidth="1"/>
+    <col min="11" max="11" width="26.44140625" customWidth="1"/>
+    <col min="12" max="12" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -733,22 +798,25 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -768,7 +836,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>11</v>
@@ -780,10 +848,13 @@
         <v>11</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -803,7 +874,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>14</v>
@@ -815,10 +886,13 @@
         <v>14</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -838,22 +912,25 @@
         <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>10001</v>
       </c>
@@ -864,19 +941,21 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5">
-        <v>200</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
       <c r="H5">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>10002</v>
       </c>
@@ -884,22 +963,22 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6">
+        <v>60</v>
+      </c>
+      <c r="H6">
         <v>300</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>15</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>10003</v>
       </c>
@@ -907,25 +986,22 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7">
+        <v>59</v>
+      </c>
+      <c r="H7">
         <v>400</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>20</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>3</v>
       </c>
-      <c r="J7">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>10004</v>
       </c>
@@ -933,25 +1009,22 @@
         <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8">
+        <v>58</v>
+      </c>
+      <c r="H8">
         <v>500</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>25</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>4</v>
       </c>
-      <c r="J8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>10005</v>
       </c>
@@ -959,204 +1032,180 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9">
+        <v>69</v>
+      </c>
+      <c r="H9">
         <v>600</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>30</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>5</v>
       </c>
-      <c r="J9">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>10006</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10">
+        <v>70</v>
+      </c>
+      <c r="H10">
         <v>250</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>11</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>1</v>
       </c>
-      <c r="J10">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>10007</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11">
+        <v>61</v>
+      </c>
+      <c r="H11">
         <v>350</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>16</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>2</v>
       </c>
-      <c r="J11">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>10008</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12">
+        <v>71</v>
+      </c>
+      <c r="H12">
         <v>450</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>21</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>3</v>
       </c>
-      <c r="J12">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10009</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13">
+        <v>62</v>
+      </c>
+      <c r="H13">
         <v>550</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>26</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>4</v>
       </c>
-      <c r="J13">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>10010</v>
       </c>
       <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
         <v>36</v>
       </c>
-      <c r="D14" t="s">
-        <v>45</v>
-      </c>
       <c r="E14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14">
+        <v>72</v>
+      </c>
+      <c r="H14">
         <v>650</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>31</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>5</v>
       </c>
-      <c r="J14">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>10011</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15">
+        <v>73</v>
+      </c>
+      <c r="H15">
         <v>300</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>12</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>1</v>
       </c>
-      <c r="J15">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>10012</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16">
+        <v>77</v>
+      </c>
+      <c r="H16">
         <v>400</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>17</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>2</v>
-      </c>
-      <c r="J16">
-        <v>2000</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
@@ -1164,25 +1213,22 @@
         <v>10013</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
+        <v>74</v>
+      </c>
+      <c r="H17">
         <v>500</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>22</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>3</v>
-      </c>
-      <c r="J17">
-        <v>3000</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
@@ -1190,25 +1236,22 @@
         <v>10014</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18">
+        <v>76</v>
+      </c>
+      <c r="H18">
         <v>600</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>27</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>4</v>
-      </c>
-      <c r="J18">
-        <v>4000</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
@@ -1216,25 +1259,22 @@
         <v>10015</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
+        <v>75</v>
+      </c>
+      <c r="H19">
         <v>700</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>32</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>5</v>
-      </c>
-      <c r="J19">
-        <v>4001</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
@@ -1242,25 +1282,22 @@
         <v>10016</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20">
+        <v>78</v>
+      </c>
+      <c r="H20">
         <v>350</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>13</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>1</v>
-      </c>
-      <c r="J20">
-        <v>2000</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
@@ -1268,25 +1305,22 @@
         <v>10017</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21">
+        <v>79</v>
+      </c>
+      <c r="H21">
         <v>450</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>18</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>2</v>
-      </c>
-      <c r="J21">
-        <v>3000</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
@@ -1294,25 +1328,22 @@
         <v>10018</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22">
+        <v>80</v>
+      </c>
+      <c r="H22">
         <v>550</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>23</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>3</v>
-      </c>
-      <c r="J22">
-        <v>4000</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
@@ -1320,25 +1351,22 @@
         <v>10019</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23">
+        <v>82</v>
+      </c>
+      <c r="H23">
         <v>650</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>28</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>4</v>
-      </c>
-      <c r="J23">
-        <v>4001</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
@@ -1346,25 +1374,22 @@
         <v>10020</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24">
+        <v>84</v>
+      </c>
+      <c r="H24">
         <v>750</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>33</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>5</v>
-      </c>
-      <c r="J24">
-        <v>1000</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
@@ -1372,25 +1397,22 @@
         <v>10021</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25">
+        <v>85</v>
+      </c>
+      <c r="H25">
         <v>400</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>14</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>1</v>
-      </c>
-      <c r="J25">
-        <v>3000</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
@@ -1398,25 +1420,22 @@
         <v>10022</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26">
+        <v>86</v>
+      </c>
+      <c r="H26">
         <v>500</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>19</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>2</v>
-      </c>
-      <c r="J26">
-        <v>4000</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
@@ -1424,25 +1443,22 @@
         <v>10023</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27">
+        <v>87</v>
+      </c>
+      <c r="H27">
         <v>600</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>24</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>3</v>
-      </c>
-      <c r="J27">
-        <v>4001</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
@@ -1450,25 +1466,22 @@
         <v>10024</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28">
+        <v>89</v>
+      </c>
+      <c r="H28">
         <v>700</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>29</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>4</v>
-      </c>
-      <c r="J28">
-        <v>1000</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -1476,25 +1489,22 @@
         <v>10025</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29">
+        <v>88</v>
+      </c>
+      <c r="H29">
         <v>800</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>34</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>5</v>
-      </c>
-      <c r="J29">
-        <v>1001</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
@@ -1502,25 +1512,22 @@
         <v>10026</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30">
+        <v>90</v>
+      </c>
+      <c r="H30">
         <v>450</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>15</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>1</v>
-      </c>
-      <c r="J30">
-        <v>4000</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
@@ -1528,25 +1535,22 @@
         <v>10027</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31">
+        <v>91</v>
+      </c>
+      <c r="H31">
         <v>550</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>20</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>2</v>
-      </c>
-      <c r="J31">
-        <v>4001</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
@@ -1554,25 +1558,22 @@
         <v>10028</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>86</v>
-      </c>
-      <c r="G32">
+        <v>92</v>
+      </c>
+      <c r="H32">
         <v>650</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>25</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>3</v>
-      </c>
-      <c r="J32">
-        <v>1000</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
@@ -1580,25 +1581,22 @@
         <v>10029</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33">
+        <v>93</v>
+      </c>
+      <c r="H33">
         <v>750</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>30</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>4</v>
-      </c>
-      <c r="J33">
-        <v>1001</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
@@ -1606,25 +1604,22 @@
         <v>10030</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>90</v>
-      </c>
-      <c r="G34">
+        <v>94</v>
+      </c>
+      <c r="H34">
         <v>850</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>35</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>5</v>
-      </c>
-      <c r="J34">
-        <v>1010</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/work.xlsx
+++ b/MiniTemplate/Datas/work.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F3EC94-2AF6-4F26-B189-7DB2CF5C8222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B12262-8DC6-4C0F-B463-1C0119BF9D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -763,22 +763,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD355D9D-C98C-47AD-A1A7-799954E007DF}">
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="54.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.77734375" customWidth="1"/>
-    <col min="7" max="7" width="21.88671875" customWidth="1"/>
-    <col min="8" max="9" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.109375" customWidth="1"/>
-    <col min="11" max="11" width="26.44140625" customWidth="1"/>
-    <col min="12" max="12" width="25.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.75" customWidth="1"/>
+    <col min="5" max="5" width="54.625" customWidth="1"/>
+    <col min="6" max="6" width="17.75" customWidth="1"/>
+    <col min="7" max="7" width="21.875" customWidth="1"/>
+    <col min="8" max="9" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.125" customWidth="1"/>
+    <col min="11" max="11" width="26.5" customWidth="1"/>
+    <col min="12" max="12" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,7 +816,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -854,7 +854,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -892,7 +892,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -930,7 +930,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>10001</v>
       </c>
@@ -946,16 +946,16 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>10002</v>
       </c>
@@ -972,13 +972,13 @@
         <v>300</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>10003</v>
       </c>
@@ -995,13 +995,13 @@
         <v>400</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>10004</v>
       </c>
@@ -1015,16 +1015,16 @@
         <v>58</v>
       </c>
       <c r="H8">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="I8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>10005</v>
       </c>
@@ -1038,16 +1038,16 @@
         <v>69</v>
       </c>
       <c r="H9">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="I9">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>10006</v>
       </c>
@@ -1061,16 +1061,16 @@
         <v>70</v>
       </c>
       <c r="H10">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>10007</v>
       </c>
@@ -1084,16 +1084,16 @@
         <v>61</v>
       </c>
       <c r="H11">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="I11">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>10008</v>
       </c>
@@ -1107,16 +1107,16 @@
         <v>71</v>
       </c>
       <c r="H12">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="I12">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>10009</v>
       </c>
@@ -1130,16 +1130,16 @@
         <v>62</v>
       </c>
       <c r="H13">
-        <v>550</v>
+        <v>1050</v>
       </c>
       <c r="I13">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>10010</v>
       </c>
@@ -1153,16 +1153,16 @@
         <v>72</v>
       </c>
       <c r="H14">
-        <v>650</v>
+        <v>1600</v>
       </c>
       <c r="I14">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>10011</v>
       </c>
@@ -1176,16 +1176,16 @@
         <v>73</v>
       </c>
       <c r="H15">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="I15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>10012</v>
       </c>
@@ -1199,16 +1199,16 @@
         <v>77</v>
       </c>
       <c r="H16">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="I16">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>10013</v>
       </c>
@@ -1222,16 +1222,16 @@
         <v>74</v>
       </c>
       <c r="H17">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="I17">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>10014</v>
       </c>
@@ -1245,16 +1245,16 @@
         <v>76</v>
       </c>
       <c r="H18">
-        <v>600</v>
+        <v>1350</v>
       </c>
       <c r="I18">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J18">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>10015</v>
       </c>
@@ -1268,16 +1268,16 @@
         <v>75</v>
       </c>
       <c r="H19">
-        <v>700</v>
+        <v>2200</v>
       </c>
       <c r="I19">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J19">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>10016</v>
       </c>
@@ -1291,16 +1291,16 @@
         <v>78</v>
       </c>
       <c r="H20">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="I20">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>10017</v>
       </c>
@@ -1314,16 +1314,16 @@
         <v>79</v>
       </c>
       <c r="H21">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="I21">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>10018</v>
       </c>
@@ -1337,16 +1337,16 @@
         <v>80</v>
       </c>
       <c r="H22">
-        <v>550</v>
+        <v>780</v>
       </c>
       <c r="I22">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>10019</v>
       </c>
@@ -1360,16 +1360,16 @@
         <v>82</v>
       </c>
       <c r="H23">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="I23">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J23">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>10020</v>
       </c>
@@ -1383,16 +1383,16 @@
         <v>84</v>
       </c>
       <c r="H24">
-        <v>750</v>
+        <v>1800</v>
       </c>
       <c r="I24">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>10021</v>
       </c>
@@ -1406,16 +1406,16 @@
         <v>85</v>
       </c>
       <c r="H25">
-        <v>400</v>
+        <v>280</v>
       </c>
       <c r="I25">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>10022</v>
       </c>
@@ -1429,16 +1429,16 @@
         <v>86</v>
       </c>
       <c r="H26">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="I26">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>10023</v>
       </c>
@@ -1452,16 +1452,16 @@
         <v>87</v>
       </c>
       <c r="H27">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="I27">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>10024</v>
       </c>
@@ -1475,16 +1475,16 @@
         <v>89</v>
       </c>
       <c r="H28">
-        <v>700</v>
+        <v>1050</v>
       </c>
       <c r="I28">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>10025</v>
       </c>
@@ -1498,16 +1498,16 @@
         <v>88</v>
       </c>
       <c r="H29">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="I29">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>10026</v>
       </c>
@@ -1521,16 +1521,16 @@
         <v>90</v>
       </c>
       <c r="H30">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="I30">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>10027</v>
       </c>
@@ -1544,16 +1544,16 @@
         <v>91</v>
       </c>
       <c r="H31">
-        <v>550</v>
+        <v>850</v>
       </c>
       <c r="I31">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>10028</v>
       </c>
@@ -1567,16 +1567,16 @@
         <v>92</v>
       </c>
       <c r="H32">
-        <v>650</v>
+        <v>1400</v>
       </c>
       <c r="I32">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>10029</v>
       </c>
@@ -1590,16 +1590,16 @@
         <v>93</v>
       </c>
       <c r="H33">
-        <v>750</v>
+        <v>2400</v>
       </c>
       <c r="I33">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>10030</v>
       </c>
@@ -1613,10 +1613,10 @@
         <v>94</v>
       </c>
       <c r="H34">
-        <v>850</v>
+        <v>4500</v>
       </c>
       <c r="I34">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J34">
         <v>5</v>

--- a/MiniTemplate/Datas/work.xlsx
+++ b/MiniTemplate/Datas/work.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B12262-8DC6-4C0F-B463-1C0119BF9D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA31A01-D6A2-45F5-9425-B378D18EF02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -375,6 +375,150 @@
   </si>
   <si>
     <t>金币数浮动区间百分比</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>unlockItemName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁道具名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电动踏板车</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>厢式货车</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建筑许可证书</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>版式启蒙册</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵感数位板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣传样机册</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>品牌识别手册</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>展陈设计证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Web三剑客教程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>微X教程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hadoop教程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MySQL教程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unity教程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_1]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_2]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_3]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_4]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础维修工具包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>管路维护套装</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>智能万用表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重型检修箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>精密校准箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵感钢笔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卖点卡册</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>采访录音笔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧本打字机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>策划档案箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时委托单</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作通行券</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特别邀请函</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目投标书</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>传奇推荐信</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -762,23 +906,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD355D9D-C98C-47AD-A1A7-799954E007DF}">
-  <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="5" width="54.625" customWidth="1"/>
-    <col min="6" max="6" width="17.75" customWidth="1"/>
-    <col min="7" max="7" width="21.875" customWidth="1"/>
-    <col min="8" max="9" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.125" customWidth="1"/>
-    <col min="11" max="11" width="26.5" customWidth="1"/>
-    <col min="12" max="12" width="25.625" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="54.6640625" customWidth="1"/>
+    <col min="6" max="6" width="55" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" customWidth="1"/>
+    <col min="8" max="9" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.109375" customWidth="1"/>
+    <col min="11" max="11" width="26.44140625" customWidth="1"/>
+    <col min="12" max="12" width="25.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,8 +960,11 @@
       <c r="L1" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -853,8 +1001,11 @@
       <c r="L2" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -891,8 +1042,11 @@
       <c r="L3" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M3" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -929,8 +1083,11 @@
       <c r="L4" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>10001</v>
       </c>
@@ -943,8 +1100,12 @@
       <c r="E5" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5</v>
+      </c>
       <c r="H5">
         <v>220</v>
       </c>
@@ -955,7 +1116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>10002</v>
       </c>
@@ -968,6 +1129,12 @@
       <c r="E6" t="s">
         <v>60</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
       <c r="H6">
         <v>300</v>
       </c>
@@ -978,7 +1145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>10003</v>
       </c>
@@ -991,6 +1158,12 @@
       <c r="E7" t="s">
         <v>59</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
       <c r="H7">
         <v>400</v>
       </c>
@@ -1000,8 +1173,14 @@
       <c r="J7">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K7">
+        <v>4000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>10004</v>
       </c>
@@ -1014,6 +1193,12 @@
       <c r="E8" t="s">
         <v>58</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
       <c r="H8">
         <v>520</v>
       </c>
@@ -1023,8 +1208,14 @@
       <c r="J8">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K8">
+        <v>4001</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>10005</v>
       </c>
@@ -1037,6 +1228,12 @@
       <c r="E9" t="s">
         <v>69</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
       <c r="H9">
         <v>680</v>
       </c>
@@ -1046,8 +1243,14 @@
       <c r="J9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K9">
+        <v>4002</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>10006</v>
       </c>
@@ -1060,6 +1263,12 @@
       <c r="E10" t="s">
         <v>70</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
       <c r="H10">
         <v>300</v>
       </c>
@@ -1069,8 +1278,14 @@
       <c r="J10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K10">
+        <v>4003</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>10007</v>
       </c>
@@ -1083,6 +1298,12 @@
       <c r="E11" t="s">
         <v>61</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
       <c r="H11">
         <v>450</v>
       </c>
@@ -1092,8 +1313,14 @@
       <c r="J11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K11">
+        <v>4004</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>10008</v>
       </c>
@@ -1106,6 +1333,12 @@
       <c r="E12" t="s">
         <v>71</v>
       </c>
+      <c r="F12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
       <c r="H12">
         <v>700</v>
       </c>
@@ -1115,8 +1348,14 @@
       <c r="J12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K12">
+        <v>4005</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10009</v>
       </c>
@@ -1129,6 +1368,12 @@
       <c r="E13" t="s">
         <v>62</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
       <c r="H13">
         <v>1050</v>
       </c>
@@ -1138,8 +1383,14 @@
       <c r="J13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K13">
+        <v>4006</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>10010</v>
       </c>
@@ -1152,6 +1403,12 @@
       <c r="E14" t="s">
         <v>72</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
       <c r="H14">
         <v>1600</v>
       </c>
@@ -1161,8 +1418,14 @@
       <c r="J14">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K14">
+        <v>4007</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>10011</v>
       </c>
@@ -1175,6 +1438,12 @@
       <c r="E15" t="s">
         <v>73</v>
       </c>
+      <c r="F15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
       <c r="H15">
         <v>350</v>
       </c>
@@ -1184,8 +1453,14 @@
       <c r="J15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K15">
+        <v>4008</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>10012</v>
       </c>
@@ -1198,6 +1473,12 @@
       <c r="E16" t="s">
         <v>77</v>
       </c>
+      <c r="F16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
       <c r="H16">
         <v>550</v>
       </c>
@@ -1207,8 +1488,14 @@
       <c r="J16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K16">
+        <v>4009</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>10013</v>
       </c>
@@ -1221,6 +1508,12 @@
       <c r="E17" t="s">
         <v>74</v>
       </c>
+      <c r="F17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
       <c r="H17">
         <v>850</v>
       </c>
@@ -1230,8 +1523,14 @@
       <c r="J17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K17">
+        <v>4010</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>10014</v>
       </c>
@@ -1244,6 +1543,12 @@
       <c r="E18" t="s">
         <v>76</v>
       </c>
+      <c r="F18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
       <c r="H18">
         <v>1350</v>
       </c>
@@ -1253,8 +1558,14 @@
       <c r="J18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K18">
+        <v>4011</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>10015</v>
       </c>
@@ -1267,6 +1578,12 @@
       <c r="E19" t="s">
         <v>75</v>
       </c>
+      <c r="F19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
       <c r="H19">
         <v>2200</v>
       </c>
@@ -1276,8 +1593,14 @@
       <c r="J19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K19">
+        <v>4012</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>10016</v>
       </c>
@@ -1290,6 +1613,12 @@
       <c r="E20" t="s">
         <v>78</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
       <c r="H20">
         <v>320</v>
       </c>
@@ -1299,8 +1628,14 @@
       <c r="J20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K20">
+        <v>4013</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>10017</v>
       </c>
@@ -1313,6 +1648,12 @@
       <c r="E21" t="s">
         <v>79</v>
       </c>
+      <c r="F21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
       <c r="H21">
         <v>500</v>
       </c>
@@ -1322,8 +1663,14 @@
       <c r="J21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K21">
+        <v>4014</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>10018</v>
       </c>
@@ -1336,6 +1683,12 @@
       <c r="E22" t="s">
         <v>80</v>
       </c>
+      <c r="F22" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
       <c r="H22">
         <v>780</v>
       </c>
@@ -1345,8 +1698,14 @@
       <c r="J22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K22">
+        <v>4015</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>10019</v>
       </c>
@@ -1359,6 +1718,12 @@
       <c r="E23" t="s">
         <v>82</v>
       </c>
+      <c r="F23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
       <c r="H23">
         <v>1200</v>
       </c>
@@ -1368,8 +1733,14 @@
       <c r="J23">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K23">
+        <v>4016</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>10020</v>
       </c>
@@ -1382,6 +1753,12 @@
       <c r="E24" t="s">
         <v>84</v>
       </c>
+      <c r="F24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24">
+        <v>10</v>
+      </c>
       <c r="H24">
         <v>1800</v>
       </c>
@@ -1391,8 +1768,14 @@
       <c r="J24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K24">
+        <v>4017</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>10021</v>
       </c>
@@ -1405,6 +1788,12 @@
       <c r="E25" t="s">
         <v>85</v>
       </c>
+      <c r="F25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
       <c r="H25">
         <v>280</v>
       </c>
@@ -1414,8 +1803,14 @@
       <c r="J25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K25">
+        <v>4018</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>10022</v>
       </c>
@@ -1428,6 +1823,12 @@
       <c r="E26" t="s">
         <v>86</v>
       </c>
+      <c r="F26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
+      </c>
       <c r="H26">
         <v>430</v>
       </c>
@@ -1437,8 +1838,14 @@
       <c r="J26">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K26">
+        <v>4019</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>10023</v>
       </c>
@@ -1451,6 +1858,12 @@
       <c r="E27" t="s">
         <v>87</v>
       </c>
+      <c r="F27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
       <c r="H27">
         <v>680</v>
       </c>
@@ -1460,8 +1873,14 @@
       <c r="J27">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K27">
+        <v>4020</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>10024</v>
       </c>
@@ -1474,6 +1893,12 @@
       <c r="E28" t="s">
         <v>89</v>
       </c>
+      <c r="F28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
       <c r="H28">
         <v>1050</v>
       </c>
@@ -1483,8 +1908,14 @@
       <c r="J28">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K28">
+        <v>4021</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>10025</v>
       </c>
@@ -1497,6 +1928,12 @@
       <c r="E29" t="s">
         <v>88</v>
       </c>
+      <c r="F29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
       <c r="H29">
         <v>1600</v>
       </c>
@@ -1506,8 +1943,14 @@
       <c r="J29">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K29">
+        <v>4022</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>10026</v>
       </c>
@@ -1520,6 +1963,12 @@
       <c r="E30" t="s">
         <v>90</v>
       </c>
+      <c r="F30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G30">
+        <v>15</v>
+      </c>
       <c r="H30">
         <v>500</v>
       </c>
@@ -1529,8 +1978,14 @@
       <c r="J30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="L30">
+        <v>4023</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>10027</v>
       </c>
@@ -1543,6 +1998,12 @@
       <c r="E31" t="s">
         <v>91</v>
       </c>
+      <c r="F31" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31">
+        <v>15</v>
+      </c>
       <c r="H31">
         <v>850</v>
       </c>
@@ -1552,8 +2013,14 @@
       <c r="J31">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="L31">
+        <v>4024</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>10028</v>
       </c>
@@ -1566,6 +2033,12 @@
       <c r="E32" t="s">
         <v>92</v>
       </c>
+      <c r="F32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G32">
+        <v>15</v>
+      </c>
       <c r="H32">
         <v>1400</v>
       </c>
@@ -1575,8 +2048,14 @@
       <c r="J32">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="L32">
+        <v>4025</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>10029</v>
       </c>
@@ -1589,6 +2068,12 @@
       <c r="E33" t="s">
         <v>93</v>
       </c>
+      <c r="F33" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33">
+        <v>15</v>
+      </c>
       <c r="H33">
         <v>2400</v>
       </c>
@@ -1598,8 +2083,14 @@
       <c r="J33">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="L33">
+        <v>4026</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>10030</v>
       </c>
@@ -1612,6 +2103,12 @@
       <c r="E34" t="s">
         <v>94</v>
       </c>
+      <c r="F34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34">
+        <v>15</v>
+      </c>
       <c r="H34">
         <v>4500</v>
       </c>
@@ -1620,6 +2117,12 @@
       </c>
       <c r="J34">
         <v>5</v>
+      </c>
+      <c r="L34">
+        <v>4027</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/work.xlsx
+++ b/MiniTemplate/Datas/work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA31A01-D6A2-45F5-9425-B378D18EF02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F10087-EF61-464E-A35E-7D93FFBA961C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
+    <workbookView xWindow="24" yWindow="744" windowWidth="30696" windowHeight="16536" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -96,9 +96,6 @@
     <t>零工描述</t>
   </si>
   <si>
-    <t>零工 icon 地址</t>
-  </si>
-  <si>
     <t>零工获得金币数</t>
   </si>
   <si>
@@ -446,22 +443,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_1]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_2]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_3]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_4]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>基础维修工具包</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -519,6 +500,26 @@
   </si>
   <si>
     <t>传奇推荐信</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>零工 icon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>零工获得经验数</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -906,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD355D9D-C98C-47AD-A1A7-799954E007DF}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -914,16 +915,17 @@
     <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.77734375" customWidth="1"/>
     <col min="5" max="5" width="54.6640625" customWidth="1"/>
-    <col min="6" max="6" width="55" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" customWidth="1"/>
     <col min="7" max="7" width="21.88671875" customWidth="1"/>
     <col min="8" max="9" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.109375" customWidth="1"/>
-    <col min="11" max="11" width="26.44140625" customWidth="1"/>
-    <col min="12" max="12" width="25.6640625" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" customWidth="1"/>
+    <col min="11" max="11" width="13.109375" customWidth="1"/>
+    <col min="12" max="12" width="26.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.6640625" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -943,7 +945,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -952,19 +954,22 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -981,10 +986,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>11</v>
@@ -993,19 +998,22 @@
         <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1025,7 +1033,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>14</v>
@@ -1034,19 +1042,22 @@
         <v>14</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1063,45 +1074,48 @@
         <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="M4" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>10001</v>
       </c>
       <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
       <c r="E5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>116</v>
+        <v>67</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1000</v>
       </c>
       <c r="G5" s="2">
         <v>5</v>
@@ -1113,24 +1127,27 @@
         <v>8</v>
       </c>
       <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>10002</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>116</v>
+        <v>59</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1000</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1142,24 +1159,27 @@
         <v>10</v>
       </c>
       <c r="J6">
+        <v>30</v>
+      </c>
+      <c r="K6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>10003</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>116</v>
+        <v>58</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1000</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1171,30 +1191,33 @@
         <v>12</v>
       </c>
       <c r="J7">
+        <v>45</v>
+      </c>
+      <c r="K7">
         <v>3</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>4000</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>10004</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>117</v>
+        <v>57</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1001</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1206,30 +1229,33 @@
         <v>15</v>
       </c>
       <c r="J8">
+        <v>65</v>
+      </c>
+      <c r="K8">
         <v>4</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>4001</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>10005</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>117</v>
+        <v>68</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1001</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1241,30 +1267,33 @@
         <v>18</v>
       </c>
       <c r="J9">
+        <v>90</v>
+      </c>
+      <c r="K9">
         <v>5</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>4002</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>10006</v>
       </c>
       <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
       <c r="E10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>116</v>
+        <v>69</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1000</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -1276,30 +1305,33 @@
         <v>5</v>
       </c>
       <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10">
         <v>1</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>4003</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>10007</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>116</v>
+        <v>60</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1000</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -1311,30 +1343,33 @@
         <v>6</v>
       </c>
       <c r="J11">
+        <v>30</v>
+      </c>
+      <c r="K11">
         <v>2</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>4004</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>10008</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>117</v>
+        <v>70</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1001</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1346,30 +1381,33 @@
         <v>8</v>
       </c>
       <c r="J12">
+        <v>45</v>
+      </c>
+      <c r="K12">
         <v>3</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>4005</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N12" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10009</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>118</v>
+        <v>61</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1002</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -1381,30 +1419,33 @@
         <v>10</v>
       </c>
       <c r="J13">
+        <v>65</v>
+      </c>
+      <c r="K13">
         <v>4</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>4006</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N13" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>10010</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>118</v>
+        <v>71</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1002</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1416,30 +1457,33 @@
         <v>12</v>
       </c>
       <c r="J14">
+        <v>90</v>
+      </c>
+      <c r="K14">
         <v>5</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>4007</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N14" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>10011</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>116</v>
+        <v>72</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1000</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -1451,30 +1495,33 @@
         <v>6</v>
       </c>
       <c r="J15">
+        <v>20</v>
+      </c>
+      <c r="K15">
         <v>1</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>4008</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N15" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>10012</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>117</v>
+        <v>76</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1001</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -1486,30 +1533,33 @@
         <v>7</v>
       </c>
       <c r="J16">
+        <v>30</v>
+      </c>
+      <c r="K16">
         <v>2</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>4009</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N16" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>10013</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>117</v>
+        <v>73</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1001</v>
       </c>
       <c r="G17">
         <v>10</v>
@@ -1521,30 +1571,33 @@
         <v>9</v>
       </c>
       <c r="J17">
+        <v>45</v>
+      </c>
+      <c r="K17">
         <v>3</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>4010</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N17" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>10014</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>118</v>
+        <v>75</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1002</v>
       </c>
       <c r="G18">
         <v>10</v>
@@ -1556,30 +1609,33 @@
         <v>11</v>
       </c>
       <c r="J18">
+        <v>65</v>
+      </c>
+      <c r="K18">
         <v>4</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>4011</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N18" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>10015</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>118</v>
+        <v>74</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1002</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -1591,30 +1647,33 @@
         <v>14</v>
       </c>
       <c r="J19">
+        <v>90</v>
+      </c>
+      <c r="K19">
         <v>5</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>4012</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N19" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>10016</v>
       </c>
       <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
         <v>38</v>
       </c>
-      <c r="D20" t="s">
-        <v>39</v>
-      </c>
       <c r="E20" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>116</v>
+        <v>77</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1000</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -1626,30 +1685,33 @@
         <v>7</v>
       </c>
       <c r="J20">
+        <v>20</v>
+      </c>
+      <c r="K20">
         <v>1</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>4013</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N20" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>10017</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>117</v>
+        <v>78</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1001</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -1661,30 +1723,33 @@
         <v>9</v>
       </c>
       <c r="J21">
+        <v>30</v>
+      </c>
+      <c r="K21">
         <v>2</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>4014</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N21" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>10018</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>117</v>
+        <v>79</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1001</v>
       </c>
       <c r="G22">
         <v>10</v>
@@ -1696,30 +1761,33 @@
         <v>11</v>
       </c>
       <c r="J22">
+        <v>45</v>
+      </c>
+      <c r="K22">
         <v>3</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>4015</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N22" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>10019</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>118</v>
+        <v>81</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1002</v>
       </c>
       <c r="G23">
         <v>10</v>
@@ -1731,30 +1799,33 @@
         <v>14</v>
       </c>
       <c r="J23">
+        <v>65</v>
+      </c>
+      <c r="K23">
         <v>4</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>4016</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N23" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>10020</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>118</v>
+        <v>83</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1002</v>
       </c>
       <c r="G24">
         <v>10</v>
@@ -1766,30 +1837,33 @@
         <v>16</v>
       </c>
       <c r="J24">
+        <v>90</v>
+      </c>
+      <c r="K24">
         <v>5</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>4017</v>
       </c>
-      <c r="M24" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N24" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>10021</v>
       </c>
       <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" t="s">
         <v>42</v>
       </c>
-      <c r="D25" t="s">
-        <v>43</v>
-      </c>
       <c r="E25" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>116</v>
+        <v>84</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1000</v>
       </c>
       <c r="G25">
         <v>10</v>
@@ -1801,30 +1875,33 @@
         <v>4</v>
       </c>
       <c r="J25">
+        <v>20</v>
+      </c>
+      <c r="K25">
         <v>1</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>4018</v>
       </c>
-      <c r="M25" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N25" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>10022</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>116</v>
+        <v>85</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1000</v>
       </c>
       <c r="G26">
         <v>10</v>
@@ -1836,30 +1913,33 @@
         <v>5</v>
       </c>
       <c r="J26">
+        <v>30</v>
+      </c>
+      <c r="K26">
         <v>2</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>4019</v>
       </c>
-      <c r="M26" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N26" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>10023</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>87</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>117</v>
+        <v>86</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1001</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -1871,30 +1951,33 @@
         <v>7</v>
       </c>
       <c r="J27">
+        <v>45</v>
+      </c>
+      <c r="K27">
         <v>3</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>4020</v>
       </c>
-      <c r="M27" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N27" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>10024</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>118</v>
+        <v>88</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1002</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -1906,30 +1989,33 @@
         <v>9</v>
       </c>
       <c r="J28">
+        <v>65</v>
+      </c>
+      <c r="K28">
         <v>4</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>4021</v>
       </c>
-      <c r="M28" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N28" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>10025</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1002</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -1941,30 +2027,33 @@
         <v>11</v>
       </c>
       <c r="J29">
+        <v>90</v>
+      </c>
+      <c r="K29">
         <v>5</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>4022</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N29" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>10026</v>
       </c>
       <c r="C30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
         <v>48</v>
       </c>
-      <c r="D30" t="s">
-        <v>49</v>
-      </c>
       <c r="E30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1001</v>
       </c>
       <c r="G30">
         <v>15</v>
@@ -1976,30 +2065,33 @@
         <v>3</v>
       </c>
       <c r="J30">
+        <v>20</v>
+      </c>
+      <c r="K30">
         <v>1</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>4023</v>
       </c>
-      <c r="M30" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N30" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>10027</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>117</v>
+        <v>90</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1001</v>
       </c>
       <c r="G31">
         <v>15</v>
@@ -2011,30 +2103,33 @@
         <v>5</v>
       </c>
       <c r="J31">
+        <v>30</v>
+      </c>
+      <c r="K31">
         <v>2</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>4024</v>
       </c>
-      <c r="M31" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N31" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>10028</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>118</v>
+        <v>91</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1002</v>
       </c>
       <c r="G32">
         <v>15</v>
@@ -2046,30 +2141,33 @@
         <v>7</v>
       </c>
       <c r="J32">
+        <v>45</v>
+      </c>
+      <c r="K32">
         <v>3</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>4025</v>
       </c>
-      <c r="M32" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N32" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>10029</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E33" t="s">
-        <v>93</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>118</v>
+        <v>92</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1002</v>
       </c>
       <c r="G33">
         <v>15</v>
@@ -2081,30 +2179,33 @@
         <v>10</v>
       </c>
       <c r="J33">
+        <v>65</v>
+      </c>
+      <c r="K33">
         <v>4</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>4026</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N33" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>10030</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E34" t="s">
-        <v>94</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>119</v>
+        <v>93</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1003</v>
       </c>
       <c r="G34">
         <v>15</v>
@@ -2116,13 +2217,16 @@
         <v>15</v>
       </c>
       <c r="J34">
+        <v>90</v>
+      </c>
+      <c r="K34">
         <v>5</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>4027</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>134</v>
+      <c r="N34" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
